--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122113553</v>
+        <v>122112921</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
+        <v>56577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597484</v>
+        <v>597548</v>
       </c>
       <c r="R2" t="n">
-        <v>7035525</v>
+        <v>7035562</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122115019</v>
+        <v>122114753</v>
       </c>
       <c r="B3" t="n">
         <v>56577</v>
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597327</v>
+        <v>597319</v>
       </c>
       <c r="R3" t="n">
-        <v>7035333</v>
+        <v>7035337</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122114753</v>
+        <v>122113553</v>
       </c>
       <c r="B4" t="n">
-        <v>56577</v>
+        <v>78632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597319</v>
+        <v>597484</v>
       </c>
       <c r="R4" t="n">
-        <v>7035337</v>
+        <v>7035525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122114233</v>
+        <v>122112759</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
+        <v>56577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597364</v>
+        <v>597537</v>
       </c>
       <c r="R5" t="n">
-        <v>7035445</v>
+        <v>7035577</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122113045</v>
+        <v>122114233</v>
       </c>
       <c r="B7" t="n">
-        <v>56577</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,31 +1217,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597538</v>
+        <v>597364</v>
       </c>
       <c r="R7" t="n">
-        <v>7035545</v>
+        <v>7035445</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122112759</v>
+        <v>122113164</v>
       </c>
       <c r="B8" t="n">
         <v>56577</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597537</v>
+        <v>597535</v>
       </c>
       <c r="R8" t="n">
-        <v>7035577</v>
+        <v>7035543</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122113164</v>
+        <v>122113045</v>
       </c>
       <c r="B9" t="n">
         <v>56577</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597535</v>
+        <v>597538</v>
       </c>
       <c r="R9" t="n">
-        <v>7035543</v>
+        <v>7035545</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122112921</v>
+        <v>122115019</v>
       </c>
       <c r="B10" t="n">
         <v>56577</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597548</v>
+        <v>597327</v>
       </c>
       <c r="R10" t="n">
-        <v>7035562</v>
+        <v>7035333</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122112921</v>
+        <v>122113164</v>
       </c>
       <c r="B2" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597548</v>
+        <v>597535</v>
       </c>
       <c r="R2" t="n">
-        <v>7035562</v>
+        <v>7035543</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122114753</v>
+        <v>122114233</v>
       </c>
       <c r="B3" t="n">
-        <v>56577</v>
+        <v>57369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597319</v>
+        <v>597364</v>
       </c>
       <c r="R3" t="n">
-        <v>7035337</v>
+        <v>7035445</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113553</v>
+        <v>122112568</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
+        <v>56581</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +906,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597484</v>
+        <v>597538</v>
       </c>
       <c r="R4" t="n">
-        <v>7035525</v>
+        <v>7035597</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122112759</v>
+        <v>122113045</v>
       </c>
       <c r="B5" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597537</v>
+        <v>597538</v>
       </c>
       <c r="R5" t="n">
-        <v>7035577</v>
+        <v>7035545</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122112568</v>
+        <v>122112759</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597538</v>
+        <v>597537</v>
       </c>
       <c r="R6" t="n">
-        <v>7035597</v>
+        <v>7035577</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122114233</v>
+        <v>122114753</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
+        <v>56581</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,43 +1227,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597364</v>
+        <v>597319</v>
       </c>
       <c r="R7" t="n">
-        <v>7035445</v>
+        <v>7035337</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122113164</v>
+        <v>122115019</v>
       </c>
       <c r="B8" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,14 +1363,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597535</v>
+        <v>597327</v>
       </c>
       <c r="R8" t="n">
-        <v>7035543</v>
+        <v>7035333</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122113045</v>
+        <v>122113553</v>
       </c>
       <c r="B9" t="n">
-        <v>56577</v>
+        <v>78639</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,43 +1441,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597538</v>
+        <v>597484</v>
       </c>
       <c r="R9" t="n">
-        <v>7035545</v>
+        <v>7035525</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122115019</v>
+        <v>122112921</v>
       </c>
       <c r="B10" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597327</v>
+        <v>597548</v>
       </c>
       <c r="R10" t="n">
-        <v>7035333</v>
+        <v>7035562</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122113164</v>
+        <v>122114753</v>
       </c>
       <c r="B2" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597535</v>
+        <v>597319</v>
       </c>
       <c r="R2" t="n">
-        <v>7035543</v>
+        <v>7035337</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122114233</v>
+        <v>122112568</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>56582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597364</v>
+        <v>597538</v>
       </c>
       <c r="R3" t="n">
-        <v>7035445</v>
+        <v>7035597</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122112568</v>
+        <v>122114233</v>
       </c>
       <c r="B4" t="n">
-        <v>56581</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,31 +901,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597538</v>
+        <v>597364</v>
       </c>
       <c r="R4" t="n">
-        <v>7035597</v>
+        <v>7035445</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122113045</v>
+        <v>122113553</v>
       </c>
       <c r="B5" t="n">
-        <v>56581</v>
+        <v>78643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,43 +1013,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597538</v>
+        <v>597484</v>
       </c>
       <c r="R5" t="n">
-        <v>7035545</v>
+        <v>7035525</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122112759</v>
+        <v>122113164</v>
       </c>
       <c r="B6" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597537</v>
+        <v>597535</v>
       </c>
       <c r="R6" t="n">
-        <v>7035577</v>
+        <v>7035543</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122114753</v>
+        <v>122113045</v>
       </c>
       <c r="B7" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,14 +1251,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597319</v>
+        <v>597538</v>
       </c>
       <c r="R7" t="n">
-        <v>7035337</v>
+        <v>7035545</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1322,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122115019</v>
+        <v>122112921</v>
       </c>
       <c r="B8" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,14 +1358,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597327</v>
+        <v>597548</v>
       </c>
       <c r="R8" t="n">
-        <v>7035333</v>
+        <v>7035562</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122113553</v>
+        <v>122112759</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
+        <v>56582</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,38 +1436,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597484</v>
+        <v>597537</v>
       </c>
       <c r="R9" t="n">
-        <v>7035525</v>
+        <v>7035577</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122112921</v>
+        <v>122115019</v>
       </c>
       <c r="B10" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597548</v>
+        <v>597327</v>
       </c>
       <c r="R10" t="n">
-        <v>7035562</v>
+        <v>7035333</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122114753</v>
+        <v>122112921</v>
       </c>
       <c r="B2" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597319</v>
+        <v>597548</v>
       </c>
       <c r="R2" t="n">
-        <v>7035337</v>
+        <v>7035562</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122112568</v>
+        <v>122113553</v>
       </c>
       <c r="B3" t="n">
-        <v>56582</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597538</v>
+        <v>597484</v>
       </c>
       <c r="R3" t="n">
-        <v>7035597</v>
+        <v>7035525</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122114233</v>
+        <v>122113164</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>56584</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,31 +896,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597364</v>
+        <v>597535</v>
       </c>
       <c r="R4" t="n">
-        <v>7035445</v>
+        <v>7035543</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122113553</v>
+        <v>122114233</v>
       </c>
       <c r="B5" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597484</v>
+        <v>597364</v>
       </c>
       <c r="R5" t="n">
-        <v>7035525</v>
+        <v>7035445</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1077,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122113164</v>
+        <v>122112568</v>
       </c>
       <c r="B6" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597535</v>
+        <v>597538</v>
       </c>
       <c r="R6" t="n">
-        <v>7035543</v>
+        <v>7035597</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122113045</v>
+        <v>122112759</v>
       </c>
       <c r="B7" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597538</v>
+        <v>597537</v>
       </c>
       <c r="R7" t="n">
-        <v>7035545</v>
+        <v>7035577</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122112921</v>
+        <v>122114753</v>
       </c>
       <c r="B8" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597548</v>
+        <v>597319</v>
       </c>
       <c r="R8" t="n">
-        <v>7035562</v>
+        <v>7035337</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122112759</v>
+        <v>122115019</v>
       </c>
       <c r="B9" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,14 +1465,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597537</v>
+        <v>597327</v>
       </c>
       <c r="R9" t="n">
-        <v>7035577</v>
+        <v>7035333</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122115019</v>
+        <v>122113045</v>
       </c>
       <c r="B10" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597327</v>
+        <v>597538</v>
       </c>
       <c r="R10" t="n">
-        <v>7035333</v>
+        <v>7035545</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122112921</v>
+        <v>122114753</v>
       </c>
       <c r="B2" t="n">
         <v>56584</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597548</v>
+        <v>597319</v>
       </c>
       <c r="R2" t="n">
-        <v>7035562</v>
+        <v>7035337</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122113553</v>
+        <v>122112568</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>56584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597484</v>
+        <v>597538</v>
       </c>
       <c r="R3" t="n">
-        <v>7035525</v>
+        <v>7035597</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113164</v>
+        <v>122113553</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>78645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597535</v>
+        <v>597484</v>
       </c>
       <c r="R4" t="n">
-        <v>7035543</v>
+        <v>7035525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122114233</v>
+        <v>122112921</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597364</v>
+        <v>597548</v>
       </c>
       <c r="R5" t="n">
-        <v>7035445</v>
+        <v>7035562</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122112568</v>
+        <v>122113045</v>
       </c>
       <c r="B6" t="n">
         <v>56584</v>
@@ -1151,7 +1146,7 @@
         <v>597538</v>
       </c>
       <c r="R6" t="n">
-        <v>7035597</v>
+        <v>7035545</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122114753</v>
+        <v>122113164</v>
       </c>
       <c r="B8" t="n">
         <v>56584</v>
@@ -1358,14 +1353,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597319</v>
+        <v>597535</v>
       </c>
       <c r="R8" t="n">
-        <v>7035337</v>
+        <v>7035543</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122115019</v>
+        <v>122114233</v>
       </c>
       <c r="B9" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,43 +1431,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597327</v>
+        <v>597364</v>
       </c>
       <c r="R9" t="n">
-        <v>7035333</v>
+        <v>7035445</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122113045</v>
+        <v>122115019</v>
       </c>
       <c r="B10" t="n">
         <v>56584</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597538</v>
+        <v>597327</v>
       </c>
       <c r="R10" t="n">
-        <v>7035545</v>
+        <v>7035333</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122115019</v>
+        <v>122114233</v>
       </c>
       <c r="B2" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597327</v>
+        <v>597364</v>
       </c>
       <c r="R2" t="n">
-        <v>7035333</v>
+        <v>7035445</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122112568</v>
+        <v>122115019</v>
       </c>
       <c r="B3" t="n">
         <v>56584</v>
@@ -823,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597538</v>
+        <v>597327</v>
       </c>
       <c r="R3" t="n">
-        <v>7035597</v>
+        <v>7035333</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113045</v>
+        <v>122113553</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>78645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597538</v>
+        <v>597484</v>
       </c>
       <c r="R4" t="n">
-        <v>7035545</v>
+        <v>7035525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122113553</v>
+        <v>122112759</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>56584</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,38 +1008,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597484</v>
+        <v>597537</v>
       </c>
       <c r="R5" t="n">
-        <v>7035525</v>
+        <v>7035577</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122113164</v>
+        <v>122114753</v>
       </c>
       <c r="B6" t="n">
         <v>56584</v>
@@ -1139,14 +1144,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597535</v>
+        <v>597319</v>
       </c>
       <c r="R6" t="n">
-        <v>7035543</v>
+        <v>7035337</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122112759</v>
+        <v>122112568</v>
       </c>
       <c r="B7" t="n">
         <v>56584</v>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597537</v>
+        <v>597538</v>
       </c>
       <c r="R7" t="n">
-        <v>7035577</v>
+        <v>7035597</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122114233</v>
+        <v>122113045</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,31 +1329,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1357,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597364</v>
+        <v>597538</v>
       </c>
       <c r="R8" t="n">
-        <v>7035445</v>
+        <v>7035545</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,11 +1398,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122114753</v>
+        <v>122113164</v>
       </c>
       <c r="B10" t="n">
         <v>56584</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597319</v>
+        <v>597535</v>
       </c>
       <c r="R10" t="n">
-        <v>7035337</v>
+        <v>7035543</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122114233</v>
+        <v>122113164</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597364</v>
+        <v>597535</v>
       </c>
       <c r="R2" t="n">
-        <v>7035445</v>
+        <v>7035543</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122115019</v>
+        <v>122114233</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597327</v>
+        <v>597364</v>
       </c>
       <c r="R3" t="n">
-        <v>7035333</v>
+        <v>7035445</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113553</v>
+        <v>122112921</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>56584</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +906,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597484</v>
+        <v>597548</v>
       </c>
       <c r="R4" t="n">
-        <v>7035525</v>
+        <v>7035562</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122112759</v>
+        <v>122112568</v>
       </c>
       <c r="B5" t="n">
         <v>56584</v>
@@ -1041,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597537</v>
+        <v>597538</v>
       </c>
       <c r="R5" t="n">
-        <v>7035577</v>
+        <v>7035597</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122114753</v>
+        <v>122112759</v>
       </c>
       <c r="B6" t="n">
         <v>56584</v>
@@ -1144,14 +1149,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597319</v>
+        <v>597537</v>
       </c>
       <c r="R6" t="n">
-        <v>7035337</v>
+        <v>7035577</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122112568</v>
+        <v>122115019</v>
       </c>
       <c r="B7" t="n">
         <v>56584</v>
@@ -1251,14 +1256,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597538</v>
+        <v>597327</v>
       </c>
       <c r="R7" t="n">
-        <v>7035597</v>
+        <v>7035333</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122112921</v>
+        <v>122113553</v>
       </c>
       <c r="B9" t="n">
-        <v>56584</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,43 +1441,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597548</v>
+        <v>597484</v>
       </c>
       <c r="R9" t="n">
-        <v>7035562</v>
+        <v>7035525</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122113164</v>
+        <v>122114753</v>
       </c>
       <c r="B10" t="n">
         <v>56584</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597535</v>
+        <v>597319</v>
       </c>
       <c r="R10" t="n">
-        <v>7035543</v>
+        <v>7035337</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122113164</v>
+        <v>122115019</v>
       </c>
       <c r="B2" t="n">
         <v>56584</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597535</v>
+        <v>597327</v>
       </c>
       <c r="R2" t="n">
-        <v>7035543</v>
+        <v>7035333</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122114233</v>
+        <v>122112921</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597364</v>
+        <v>597548</v>
       </c>
       <c r="R3" t="n">
-        <v>7035445</v>
+        <v>7035562</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122112921</v>
+        <v>122113553</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,43 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597548</v>
+        <v>597484</v>
       </c>
       <c r="R4" t="n">
-        <v>7035562</v>
+        <v>7035525</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1001,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122112568</v>
+        <v>122114233</v>
       </c>
       <c r="B5" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1046,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597538</v>
+        <v>597364</v>
       </c>
       <c r="R5" t="n">
-        <v>7035597</v>
+        <v>7035445</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122112759</v>
+        <v>122113164</v>
       </c>
       <c r="B6" t="n">
         <v>56584</v>
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597537</v>
+        <v>597535</v>
       </c>
       <c r="R6" t="n">
-        <v>7035577</v>
+        <v>7035543</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1215,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122115019</v>
+        <v>122114753</v>
       </c>
       <c r="B7" t="n">
         <v>56584</v>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597327</v>
+        <v>597319</v>
       </c>
       <c r="R7" t="n">
-        <v>7035333</v>
+        <v>7035337</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1322,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122113045</v>
+        <v>122112568</v>
       </c>
       <c r="B8" t="n">
         <v>56584</v>
@@ -1370,7 +1365,7 @@
         <v>597538</v>
       </c>
       <c r="R8" t="n">
-        <v>7035545</v>
+        <v>7035597</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122113553</v>
+        <v>122112759</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>56584</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,38 +1436,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597484</v>
+        <v>597537</v>
       </c>
       <c r="R9" t="n">
-        <v>7035525</v>
+        <v>7035577</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122114753</v>
+        <v>122113045</v>
       </c>
       <c r="B10" t="n">
         <v>56584</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597319</v>
+        <v>597538</v>
       </c>
       <c r="R10" t="n">
-        <v>7035337</v>
+        <v>7035545</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122115019</v>
+        <v>122114233</v>
       </c>
       <c r="B2" t="n">
-        <v>56584</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597327</v>
+        <v>597364</v>
       </c>
       <c r="R2" t="n">
-        <v>7035333</v>
+        <v>7035445</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122112921</v>
+        <v>122113045</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597548</v>
+        <v>597538</v>
       </c>
       <c r="R3" t="n">
-        <v>7035562</v>
+        <v>7035545</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113553</v>
+        <v>122113164</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +906,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597484</v>
+        <v>597535</v>
       </c>
       <c r="R4" t="n">
-        <v>7035525</v>
+        <v>7035543</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122114233</v>
+        <v>122115019</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>56589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,43 +1013,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597364</v>
+        <v>597327</v>
       </c>
       <c r="R5" t="n">
-        <v>7035445</v>
+        <v>7035333</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,11 +1082,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122113164</v>
+        <v>122113553</v>
       </c>
       <c r="B6" t="n">
-        <v>56584</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,43 +1120,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597535</v>
+        <v>597484</v>
       </c>
       <c r="R6" t="n">
-        <v>7035543</v>
+        <v>7035525</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,7 +1213,7 @@
         <v>122114753</v>
       </c>
       <c r="B7" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>122112568</v>
       </c>
       <c r="B8" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122112759</v>
+        <v>122112921</v>
       </c>
       <c r="B9" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597537</v>
+        <v>597548</v>
       </c>
       <c r="R9" t="n">
-        <v>7035577</v>
+        <v>7035562</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122113045</v>
+        <v>122112759</v>
       </c>
       <c r="B10" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597538</v>
+        <v>597537</v>
       </c>
       <c r="R10" t="n">
-        <v>7035545</v>
+        <v>7035577</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122114233</v>
+        <v>122112759</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597364</v>
+        <v>597537</v>
       </c>
       <c r="R2" t="n">
-        <v>7035445</v>
+        <v>7035577</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122113045</v>
+        <v>122112568</v>
       </c>
       <c r="B3" t="n">
         <v>56589</v>
@@ -835,7 +830,7 @@
         <v>597538</v>
       </c>
       <c r="R3" t="n">
-        <v>7035545</v>
+        <v>7035597</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122115019</v>
+        <v>122112921</v>
       </c>
       <c r="B5" t="n">
         <v>56589</v>
@@ -1042,14 +1037,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597327</v>
+        <v>597548</v>
       </c>
       <c r="R5" t="n">
-        <v>7035333</v>
+        <v>7035562</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122113553</v>
+        <v>122114753</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>56589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,38 +1115,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597484</v>
+        <v>597319</v>
       </c>
       <c r="R6" t="n">
-        <v>7035525</v>
+        <v>7035337</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122114753</v>
+        <v>122113553</v>
       </c>
       <c r="B7" t="n">
-        <v>56589</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,43 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597319</v>
+        <v>597484</v>
       </c>
       <c r="R7" t="n">
-        <v>7035337</v>
+        <v>7035525</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122112568</v>
+        <v>122114233</v>
       </c>
       <c r="B8" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,31 +1324,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597538</v>
+        <v>597364</v>
       </c>
       <c r="R8" t="n">
-        <v>7035597</v>
+        <v>7035445</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122112921</v>
+        <v>122113045</v>
       </c>
       <c r="B9" t="n">
         <v>56589</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597548</v>
+        <v>597538</v>
       </c>
       <c r="R9" t="n">
-        <v>7035562</v>
+        <v>7035545</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122112759</v>
+        <v>122115019</v>
       </c>
       <c r="B10" t="n">
         <v>56589</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597537</v>
+        <v>597327</v>
       </c>
       <c r="R10" t="n">
-        <v>7035577</v>
+        <v>7035333</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122112759</v>
+        <v>122113553</v>
       </c>
       <c r="B2" t="n">
-        <v>56589</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597537</v>
+        <v>597484</v>
       </c>
       <c r="R2" t="n">
-        <v>7035577</v>
+        <v>7035525</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -800,11 +790,6 @@
       <c r="E3" t="n">
         <v>100138</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -907,11 +892,6 @@
       <c r="E4" t="n">
         <v>100138</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -996,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122112921</v>
+        <v>122114233</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,31 +988,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1041,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597548</v>
+        <v>597364</v>
       </c>
       <c r="R5" t="n">
-        <v>7035562</v>
+        <v>7035445</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1077,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122114753</v>
+        <v>122115019</v>
       </c>
       <c r="B6" t="n">
         <v>56589</v>
@@ -1121,11 +1101,6 @@
       <c r="E6" t="n">
         <v>100138</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -1148,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597319</v>
+        <v>597327</v>
       </c>
       <c r="R6" t="n">
-        <v>7035337</v>
+        <v>7035333</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122113553</v>
+        <v>122112759</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>56589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597484</v>
+        <v>597537</v>
       </c>
       <c r="R7" t="n">
-        <v>7035525</v>
+        <v>7035577</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122114233</v>
+        <v>122112921</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,31 +1299,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1357,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597364</v>
+        <v>597548</v>
       </c>
       <c r="R8" t="n">
-        <v>7035445</v>
+        <v>7035562</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,11 +1407,6 @@
       <c r="E9" t="n">
         <v>100138</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -1531,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122115019</v>
+        <v>122114753</v>
       </c>
       <c r="B10" t="n">
         <v>56589</v>
@@ -1549,11 +1509,6 @@
       <c r="E10" t="n">
         <v>100138</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -1576,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597327</v>
+        <v>597319</v>
       </c>
       <c r="R10" t="n">
-        <v>7035333</v>
+        <v>7035337</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113164</v>
+        <v>122114233</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,26 +886,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597535</v>
+        <v>597364</v>
       </c>
       <c r="R4" t="n">
-        <v>7035543</v>
+        <v>7035445</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122114233</v>
+        <v>122113164</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -988,26 +993,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1016,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597364</v>
+        <v>597535</v>
       </c>
       <c r="R5" t="n">
-        <v>7035445</v>
+        <v>7035543</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1052,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122114233</v>
+        <v>122113164</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,26 +886,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597364</v>
+        <v>597535</v>
       </c>
       <c r="R4" t="n">
-        <v>7035445</v>
+        <v>7035543</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -950,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122113164</v>
+        <v>122114233</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,26 +988,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1021,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597535</v>
+        <v>597364</v>
       </c>
       <c r="R5" t="n">
-        <v>7035543</v>
+        <v>7035445</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack gran, hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57101-2024 artfynd.xlsx
+++ b/artfynd/A 57101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122113553</v>
+        <v>122113164</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597484</v>
+        <v>597535</v>
       </c>
       <c r="R2" t="n">
-        <v>7035525</v>
+        <v>7035543</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122112568</v>
+        <v>122114753</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +800,11 @@
       <c r="E3" t="n">
         <v>100138</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -808,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597538</v>
+        <v>597319</v>
       </c>
       <c r="R3" t="n">
-        <v>7035597</v>
+        <v>7035337</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122113164</v>
+        <v>122115019</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,6 +907,11 @@
       <c r="E4" t="n">
         <v>100138</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -910,14 +930,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
+          <t>Nybrännberget, Nybrännberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597535</v>
+        <v>597327</v>
       </c>
       <c r="R4" t="n">
-        <v>7035543</v>
+        <v>7035333</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +999,7 @@
         <v>122114233</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,6 +1013,11 @@
       </c>
       <c r="E5" t="n">
         <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1083,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122115019</v>
+        <v>122113553</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1120,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597327</v>
+        <v>597484</v>
       </c>
       <c r="R6" t="n">
-        <v>7035333</v>
+        <v>7035525</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1188,7 +1213,7 @@
         <v>122112759</v>
       </c>
       <c r="B7" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,6 +1227,11 @@
       </c>
       <c r="E7" t="n">
         <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1290,7 +1320,7 @@
         <v>122112921</v>
       </c>
       <c r="B8" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,6 +1334,11 @@
       </c>
       <c r="E8" t="n">
         <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1392,7 +1427,7 @@
         <v>122113045</v>
       </c>
       <c r="B9" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,6 +1441,11 @@
       </c>
       <c r="E9" t="n">
         <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1491,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122114753</v>
+        <v>122112568</v>
       </c>
       <c r="B10" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1509,6 +1549,11 @@
       <c r="E10" t="n">
         <v>100138</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -1527,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybrännberget, Nybrännberget, Ång</t>
+          <t>Josef-Pettersmyran, Josef-Pettersmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597319</v>
+        <v>597538</v>
       </c>
       <c r="R10" t="n">
-        <v>7035337</v>
+        <v>7035597</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
